--- a/vse-loti/341025682/spec-341025682.xlsx
+++ b/vse-loti/341025682/spec-341025682.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +96,9 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1184,18 +1187,25 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>НДС 22 %, ставка из документа: "Ставка НДС, % — 22" — Obosnovanie N(M)TsK .xlsx; суммы источника указаны с НДС: "Кол-во ЕИ Цена за ЕИ, согласно информации, полученной заказчиком, с учетом НДС, руб." — NMTsK.txt. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Источник: Извещение о проведении электронного аукциона от 18.09.2026 №0142200001326017729.htm</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28"/>
+    <row r="29"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:B28"/>
+    <mergeCell ref="A27:B29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341025682/spec-341025682.xlsx
+++ b/vse-loti/341025682/spec-341025682.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.####"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -83,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,6 +94,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -469,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -481,6 +483,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -516,17 +519,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -549,11 +557,14 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" s="4" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
         <v>11964.1</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" s="4" t="n">
+        <v>14596.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -574,11 +585,14 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
         <v>50765.9</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" s="4" t="n">
+        <v>61934.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -606,13 +620,16 @@
         <v>0.256</v>
       </c>
       <c r="G4" s="4" t="n">
+        <v>77726.56</v>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>19898.36</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>77726.56</v>
       </c>
       <c r="I4" s="4" t="n">
         <v>94826.41</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>24276</v>
       </c>
     </row>
     <row r="5">
@@ -641,13 +658,16 @@
         <v>0.332</v>
       </c>
       <c r="G5" s="4" t="n">
+        <v>82156.63</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>27275.41</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>82156.63</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>100231.08</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>33276</v>
       </c>
     </row>
     <row r="6">
@@ -676,13 +696,16 @@
         <v>0.192</v>
       </c>
       <c r="G6" s="4" t="n">
+        <v>124367.19</v>
+      </c>
+      <c r="H6" s="4" t="n">
         <v>23878.28</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>124367.19</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>151727.97</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>29131.5</v>
       </c>
     </row>
     <row r="7">
@@ -711,13 +734,16 @@
         <v>0.239</v>
       </c>
       <c r="G7" s="4" t="n">
+        <v>79757.32000000001</v>
+      </c>
+      <c r="H7" s="4" t="n">
         <v>19062.3</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>79757.32000000001</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>97303.92999999999</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>23256.01</v>
       </c>
     </row>
     <row r="8">
@@ -746,13 +772,16 @@
         <v>0.133</v>
       </c>
       <c r="G8" s="4" t="n">
+        <v>134710.84</v>
+      </c>
+      <c r="H8" s="4" t="n">
         <v>17889.84</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>134710.84</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>164347.23</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>21825.6</v>
       </c>
     </row>
     <row r="9">
@@ -781,13 +810,16 @@
         <v>0.143</v>
       </c>
       <c r="G9" s="4" t="n">
+        <v>135589.96</v>
+      </c>
+      <c r="H9" s="4" t="n">
         <v>19443.44</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>135589.96</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>165419.75</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>23721</v>
       </c>
     </row>
     <row r="10">
@@ -816,13 +848,16 @@
         <v>0.618</v>
       </c>
       <c r="G10" s="4" t="n">
+        <v>138605.18</v>
+      </c>
+      <c r="H10" s="4" t="n">
         <v>85657.38</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>138605.18</v>
       </c>
       <c r="I10" s="4" t="n">
         <v>169098.32</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>104502</v>
       </c>
     </row>
     <row r="11">
@@ -851,13 +886,16 @@
         <v>0.192</v>
       </c>
       <c r="G11" s="4" t="n">
+        <v>154468.75</v>
+      </c>
+      <c r="H11" s="4" t="n">
         <v>29658.2</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>154468.75</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>188451.88</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>36183</v>
       </c>
     </row>
     <row r="12">
@@ -886,13 +924,16 @@
         <v>0.282</v>
       </c>
       <c r="G12" s="4" t="n">
+        <v>100466.67</v>
+      </c>
+      <c r="H12" s="4" t="n">
         <v>28331.48</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>100466.67</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>122569.33</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>34564.41</v>
       </c>
     </row>
     <row r="13">
@@ -921,13 +962,16 @@
         <v>0.608</v>
       </c>
       <c r="G13" s="4" t="n">
+        <v>91634.57000000001</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>55668.03</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>91634.57000000001</v>
       </c>
       <c r="I13" s="4" t="n">
         <v>111794.17</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>67915</v>
       </c>
     </row>
     <row r="14">
@@ -956,13 +1000,16 @@
         <v>0.705</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>160746.1</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>113326.23</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>160746.1</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>196110.24</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>138258</v>
       </c>
     </row>
     <row r="15">
@@ -991,13 +1038,16 @@
         <v>0.667</v>
       </c>
       <c r="G15" s="4" t="n">
+        <v>136065.95</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>90782.95</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>136065.95</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>166000.46</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>110755.2</v>
       </c>
     </row>
     <row r="16">
@@ -1026,13 +1076,16 @@
         <v>0.834</v>
       </c>
       <c r="G16" s="4" t="n">
+        <v>155593.53</v>
+      </c>
+      <c r="H16" s="4" t="n">
         <v>129764.75</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>155593.53</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>189824.1</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>158312.99</v>
       </c>
     </row>
     <row r="17">
@@ -1058,11 +1111,14 @@
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" s="4" t="n">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" s="4" t="n">
+        <v>7320</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1087,11 +1143,14 @@
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" s="4" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="4" t="n">
         <v>1148.07</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" s="4" t="n">
+        <v>1400.65</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1116,11 +1175,14 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" s="4" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
         <v>10400</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" s="4" t="n">
+        <v>12688</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1141,71 +1203,855 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" s="4" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
         <v>4750</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" s="4" t="n">
+        <v>5795</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="n">
+          <t>Прочие позиции лота (30) — не трубы, в трубную часть и в цену за тонну не входят</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Арматура к смывному баку</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>5327.87</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Колено вертикального выпуска для чаши унитаза</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>9500</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>11590</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Кран</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1620</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>1976.4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Крышка-сиденье</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>237000</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>289140</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Лист нержавеющий</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>34133.77</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>41643.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Муфта проходная</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1850</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Писсуар</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>27750.02</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>33855.02</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Полоса прокатная</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="7" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>7315.57</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>8925</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Полуфабрикаты из меди или медных сплавов</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Полуфабрикаты из меди или медных сплавов</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>29280</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Полуфабрикаты из меди или медных сплавов</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>24950</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>30439</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Полуфабрикаты из меди или медных сплавов</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>9516</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Полуфабрикаты из меди или медных сплавов</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>35500</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>43310</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Прокат листовой стальной горячекатаный</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="7" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>38040.98</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>46410</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Прокат листовой стальной горячекатаный</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>120382.32</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>146866.43</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Прокат листовой стальной с рифлением</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>т</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>35532.79</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>43350</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Прокат листовой холоднокатаный</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Лист</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>78688.52</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>95999.99000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Раковина</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>61475.41</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Розетка штепсельная</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>8032.79</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Сифон сантехнический</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>9836.07</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>12000.01</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Стойка для душа</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>26840</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Трубы и профили пустотелые из чугуна</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>38400</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>46848</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Уголок стальной</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>26606.95</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>32460.48</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Уголок стальной</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>38151.89</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>46545.31</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Унитаз</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>13510.98</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>16483.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Унитаз</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>55450.82</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>67650</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Унитаз</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>61844.26</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>75450</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Фитинги для труб из чугуна</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>2200</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Части кранов, клапанов и аналогичной арматуры</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>10065</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>12279.3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Швеллер стальной горячекатаный</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>26147.21</v>
+      </c>
+      <c r="J51" s="4" t="n">
+        <v>31899.6</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>ИТОГО трубная часть</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
         <v>5.201</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G52" s="9" t="n">
+        <v>143369.49</v>
+      </c>
+      <c r="H52" s="9" t="n">
         <v>745664.72</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="I52" s="9" t="n">
+        <v>174910.78</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>909710.96</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>ВСЕГО по лоту (трубы + прочее)</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>1846777.94</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>2253069.09</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="H54" s="9" t="n">
         <v>1846777.93</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>НМЦК с НДС 22%:</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="J55" s="9" t="n">
         <v>2253069.08</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Трубная часть лота: 19 из 49 позиций; остальное — не трубы (арматура, колено, кран, крышка-сиденье, лист, муфта, …), в таблицу не включено. ИТОГО — только трубная часть, «НМЦК из обоснования» — весь лот. Доля трубной части в НМЦК: 40.38 %.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Трубная часть лота: 19 из 49 позиций; остальное — не трубы (арматура, колено, кран, крышка-сиденье, лист, муфта, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции. Доля трубной части в НМЦК: 40.38 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>НДС 22 %, ставка из документа: "Ставка НДС, % — 22" — Obosnovanie N(M)TsK .xlsx; суммы источника указаны с НДС: "Кол-во ЕИ Цена за ЕИ, согласно информации, полученной заказчиком, с учетом НДС, руб." — NMTsK.txt. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Источник: Извещение о проведении электронного аукциона от 18.09.2026 №0142200001326017729.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>Источник: Извещение о проведении электронного аукциона от 18.09.2026 №0142200001326017729.htm
+Почему извещение, а не спецификация: это совместные торги — в лоте 10 отдельных обоснований НМЦК, каждое описывает долю одного заказчика, и ни одно не описывает лот целиком. Все позиции сведены только в таблице «Объект закупки» печатной формы извещения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A27:B29"/>
+  <mergeCells count="2">
+    <mergeCell ref="A59:B61"/>
+    <mergeCell ref="A21:J21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341025682/spec-341025682.xlsx
+++ b/vse-loti/341025682/spec-341025682.xlsx
@@ -1185,52 +1185,49 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Фитинги для труб и трубок литые стальные</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="4" t="n">
-        <v>4750</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" s="4" t="n">
-        <v>5795</v>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Прочие позиции лота (31) — не трубы, в трубную часть и в цену за тонну не входят</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Прочие позиции лота (30) — не трубы, в трубную часть и в цену за тонну не входят</t>
-        </is>
+      <c r="A21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Арматура к смывному баку</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>5327.87</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>6500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Арматура к смывному баку</t>
+          <t>Колено вертикального выпуска для чаши унитаза</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1238,24 +1235,24 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>5327.87</v>
+        <v>9500</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>6500</v>
+        <v>11590</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Колено вертикального выпуска для чаши унитаза</t>
+          <t>Кран</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr"/>
       <c r="D23" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1263,24 +1260,24 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>9500</v>
+        <v>1620</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>11590</v>
+        <v>1976.4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Кран</t>
+          <t>Крышка-сиденье</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr"/>
       <c r="D24" s="3" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1288,24 +1285,24 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1620</v>
+        <v>237000</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1976.4</v>
+        <v>289140</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Крышка-сиденье</t>
+          <t>Лист нержавеющий</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
       <c r="D25" s="3" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -1313,24 +1310,24 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>237000</v>
+        <v>34133.77</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>289140</v>
+        <v>41643.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Лист нержавеющий</t>
+          <t>Муфта проходная</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr"/>
       <c r="D26" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -1338,24 +1335,24 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>34133.77</v>
+        <v>1850</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>41643.2</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Муфта проходная</t>
+          <t>Писсуар</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -1363,65 +1360,65 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1850</v>
+        <v>27750.02</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2257</v>
+        <v>33855.02</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Писсуар</t>
+          <t>Полоса прокатная</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="3" t="n">
-        <v>9</v>
+      <c r="D28" s="7" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>т</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>27750.02</v>
+        <v>7315.57</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>33855.02</v>
+        <v>8925</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Полоса прокатная</t>
+          <t>Полуфабрикаты из меди или медных сплавов</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="7" t="n">
-        <v>0.07000000000000001</v>
+      <c r="D29" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7315.57</v>
+        <v>38000</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8925</v>
+        <v>46360</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
@@ -1430,7 +1427,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr"/>
       <c r="D30" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -1438,15 +1435,15 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>38000</v>
+        <v>24000</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>46360</v>
+        <v>29280</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
@@ -1463,15 +1460,15 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>24000</v>
+        <v>24950</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>29280</v>
+        <v>30439</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
@@ -1480,23 +1477,23 @@
       </c>
       <c r="C32" s="2" t="inlineStr"/>
       <c r="D32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>24950</v>
+        <v>7800</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>30439</v>
+        <v>9516</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
@@ -1505,7 +1502,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr"/>
       <c r="D33" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -1513,40 +1510,40 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>7800</v>
+        <v>35500</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9516</v>
+        <v>43310</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Полуфабрикаты из меди или медных сплавов</t>
+          <t>Прокат листовой стальной горячекатаный</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="3" t="n">
-        <v>10</v>
+      <c r="D34" s="7" t="n">
+        <v>0.35</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>т</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>35500</v>
+        <v>38040.98</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>43310</v>
+        <v>46410</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
@@ -1555,7 +1552,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr"/>
       <c r="D35" s="7" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -1563,24 +1560,24 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>38040.98</v>
+        <v>120382.32</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>46410</v>
+        <v>146866.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Прокат листовой стальной горячекатаный</t>
+          <t>Прокат листовой стальной с рифлением</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="7" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -1588,74 +1585,74 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>120382.32</v>
+        <v>35532.79</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>146866.43</v>
+        <v>43350</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Прокат листовой стальной с рифлением</t>
+          <t>Прокат листовой холоднокатаный</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="7" t="n">
-        <v>0.3</v>
+      <c r="D37" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>т</t>
+          <t>Лист</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>35532.79</v>
+        <v>78688.52</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>43350</v>
+        <v>95999.99000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Прокат листовой холоднокатаный</t>
+          <t>Раковина</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Лист</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>78688.52</v>
+        <v>61475.41</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>95999.99000000001</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Раковина</t>
+          <t>Розетка штепсельная</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr"/>
       <c r="D39" s="3" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -1663,24 +1660,24 @@
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>61475.41</v>
+        <v>8032.79</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>75000</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Розетка штепсельная</t>
+          <t>Сифон сантехнический</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="3" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -1688,24 +1685,24 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>8032.79</v>
+        <v>9836.07</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>9800</v>
+        <v>12000.01</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Сифон сантехнический</t>
+          <t>Стойка для душа</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -1713,49 +1710,49 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>9836.07</v>
+        <v>22000</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>12000.01</v>
+        <v>26840</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Стойка для душа</t>
+          <t>Трубы и профили пустотелые из чугуна</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>22000</v>
+        <v>38400</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>26840</v>
+        <v>46848</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Трубы и профили пустотелые из чугуна</t>
+          <t>Уголок стальной</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="3" t="n">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -1763,15 +1760,15 @@
         </is>
       </c>
       <c r="H43" s="4" t="n">
-        <v>38400</v>
+        <v>26606.95</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>46848</v>
+        <v>32460.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
@@ -1780,7 +1777,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="3" t="n">
-        <v>156</v>
+        <v>90</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -1788,40 +1785,40 @@
         </is>
       </c>
       <c r="H44" s="4" t="n">
-        <v>26606.95</v>
+        <v>38151.89</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>32460.48</v>
+        <v>46545.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Уголок стальной</t>
+          <t>Унитаз</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="3" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="H45" s="4" t="n">
-        <v>38151.89</v>
+        <v>13510.98</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>46545.31</v>
+        <v>16483.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
@@ -1830,7 +1827,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr"/>
       <c r="D46" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -1838,15 +1835,15 @@
         </is>
       </c>
       <c r="H46" s="4" t="n">
-        <v>13510.98</v>
+        <v>55450.82</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>16483.4</v>
+        <v>67650</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
@@ -1863,24 +1860,24 @@
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>55450.82</v>
+        <v>61844.26</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>67650</v>
+        <v>75450</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Унитаз</t>
+          <t>Фитинги для труб из чугуна</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -1888,24 +1885,24 @@
         </is>
       </c>
       <c r="H48" s="4" t="n">
-        <v>61844.26</v>
+        <v>2200</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>75450</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Фитинги для труб из чугуна</t>
+          <t>Фитинги для труб и трубок литые стальные</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr"/>
       <c r="D49" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -1913,10 +1910,10 @@
         </is>
       </c>
       <c r="H49" s="4" t="n">
-        <v>2200</v>
+        <v>4750</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>2684</v>
+        <v>5795</v>
       </c>
     </row>
     <row r="50">
@@ -1979,16 +1976,16 @@
         <v>5.201</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>143369.49</v>
+        <v>142456.2</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>745664.72</v>
+        <v>740914.72</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>174910.78</v>
+        <v>173796.56</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>909710.96</v>
+        <v>903915.96</v>
       </c>
     </row>
     <row r="53">
@@ -2027,7 +2024,7 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>Трубная часть лота: 19 из 49 позиций; остальное — не трубы (арматура, колено, кран, крышка-сиденье, лист, муфта, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции. Доля трубной части в НМЦК: 40.38 %.</t>
+          <t>Трубная часть лота: 18 из 49 позиций; остальное — не трубы (арматура, колено, кран, крышка-сиденье, лист, муфта, …) — показано ниже отдельным блоком, без массы и цены за тонну. «ИТОГО трубная часть» — только трубы, «ВСЕГО по лоту» — все позиции. Доля трубной части в НМЦК: 40.12 %.</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2048,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A59:B61"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A20:J20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
